--- a/public/templates/template-siswa.xlsx
+++ b/public/templates/template-siswa.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30527"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\simakin-api\public\templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE122A3F-A268-4B48-8370-CF89C7345456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
   <si>
     <t>nis</t>
   </si>
@@ -51,22 +56,134 @@
   </si>
   <si>
     <t>alamat_ortu</t>
+  </si>
+  <si>
+    <t>Tes Nama 1</t>
+  </si>
+  <si>
+    <t>Tes Nama 2</t>
+  </si>
+  <si>
+    <t>Tes Nama 3</t>
+  </si>
+  <si>
+    <t>Tes Nama 4</t>
+  </si>
+  <si>
+    <t>Tes Nama 5</t>
+  </si>
+  <si>
+    <t>Laki-Laki</t>
+  </si>
+  <si>
+    <t>Perempuan</t>
+  </si>
+  <si>
+    <t>Tes</t>
+  </si>
+  <si>
+    <t>2026/2027</t>
+  </si>
+  <si>
+    <t>2026/2028</t>
+  </si>
+  <si>
+    <t>2026/2029</t>
+  </si>
+  <si>
+    <t>2026/2030</t>
+  </si>
+  <si>
+    <t>2026/2031</t>
+  </si>
+  <si>
+    <t>siswa1@example.com</t>
+  </si>
+  <si>
+    <t>siswa2@example.com</t>
+  </si>
+  <si>
+    <t>siswa3@example.com</t>
+  </si>
+  <si>
+    <t>siswa4@example.com</t>
+  </si>
+  <si>
+    <t>siswa5@example.com</t>
+  </si>
+  <si>
+    <t>Alamat 1</t>
+  </si>
+  <si>
+    <t>Alamat 2</t>
+  </si>
+  <si>
+    <t>Alamat 3</t>
+  </si>
+  <si>
+    <t>Alamat 4</t>
+  </si>
+  <si>
+    <t>Alamat 5</t>
+  </si>
+  <si>
+    <t>Nama Ortu 1</t>
+  </si>
+  <si>
+    <t>Nama Ortu 2</t>
+  </si>
+  <si>
+    <t>Nama Ortu 3</t>
+  </si>
+  <si>
+    <t>Nama Ortu 4</t>
+  </si>
+  <si>
+    <t>Nama Ortu 5</t>
+  </si>
+  <si>
+    <t>Alamat Ortu 1</t>
+  </si>
+  <si>
+    <t>Alamat Ortu 2</t>
+  </si>
+  <si>
+    <t>Alamat Ortu 3</t>
+  </si>
+  <si>
+    <t>Alamat Ortu 4</t>
+  </si>
+  <si>
+    <t>Alamat Ortu 5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -86,17 +203,31 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -386,14 +517,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="12.53125" customWidth="1"/>
+    <col min="3" max="3" width="23.06640625" customWidth="1"/>
+    <col min="6" max="6" width="14.46484375" customWidth="1"/>
+    <col min="7" max="7" width="13.86328125" customWidth="1"/>
+    <col min="8" max="8" width="20.53125" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="19.19921875" customWidth="1"/>
+    <col min="11" max="11" width="16.33203125" customWidth="1"/>
+    <col min="12" max="12" width="14.265625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -431,9 +570,205 @@
         <v>11</v>
       </c>
     </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>202601</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="2">
+        <v>81234567890</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2">
+        <v>81134567890</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>202602</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3">
+        <v>81234567891</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3">
+        <v>81134567891</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>202603</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="2">
+        <v>81234567892</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4">
+        <v>81134567892</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>202604</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5">
+        <v>81234567893</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5">
+        <v>81134567893</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>202605</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="2">
+        <v>81234567894</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6">
+        <v>81134567894</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{D93793CC-6FAD-4B41-934C-CF1546BE3EA3}"/>
+    <hyperlink ref="H3" r:id="rId2" xr:uid="{F31DD27A-AF44-4FFF-B3F8-38183B252DAB}"/>
+    <hyperlink ref="H4" r:id="rId3" xr:uid="{DF891447-A113-4822-A001-F74FE265C695}"/>
+    <hyperlink ref="H6" r:id="rId4" xr:uid="{C1B59141-63EF-4711-A03F-896C7012A467}"/>
+    <hyperlink ref="H5" r:id="rId5" xr:uid="{345BD270-FA97-4A93-96E2-9AD9052CABAC}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>